--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N144_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N144_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>47.11042329757886</v>
+        <v>7.655443785856566</v>
       </c>
       <c r="D2" t="n">
-        <v>46.13306665918787</v>
+        <v>7.496623332118029</v>
       </c>
       <c r="E2" t="n">
-        <v>17.89116063448317</v>
+        <v>2.907313603103515</v>
       </c>
       <c r="F2" t="n">
-        <v>15.59864920617222</v>
+        <v>2.534780496002985</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.0671778949391</v>
+        <v>3.260916407927605</v>
       </c>
       <c r="D3" t="n">
-        <v>19.31416827414492</v>
+        <v>3.138552344548549</v>
       </c>
       <c r="E3" t="n">
-        <v>17.89116063448317</v>
+        <v>2.907313603103515</v>
       </c>
       <c r="F3" t="n">
-        <v>15.59864920617222</v>
+        <v>2.534780496002985</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>43.79124354989084</v>
+        <v>7.116077076857261</v>
       </c>
       <c r="D4" t="n">
-        <v>42.83599196346007</v>
+        <v>6.960848694062261</v>
       </c>
       <c r="E4" t="n">
-        <v>17.89116063448317</v>
+        <v>2.907313603103515</v>
       </c>
       <c r="F4" t="n">
-        <v>15.59864920617222</v>
+        <v>2.534780496002985</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>13.45110847113954</v>
+        <v>2.185805126560175</v>
       </c>
       <c r="D5" t="n">
-        <v>12.47442246450414</v>
+        <v>2.027093650481922</v>
       </c>
       <c r="E5" t="n">
-        <v>17.89116063448317</v>
+        <v>2.907313603103515</v>
       </c>
       <c r="F5" t="n">
-        <v>15.59864920617222</v>
+        <v>2.534780496002985</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>14.27258876740505</v>
+        <v>2.319295674703321</v>
       </c>
       <c r="D6" t="n">
-        <v>18.96606375518641</v>
+        <v>3.081985360217792</v>
       </c>
       <c r="E6" t="n">
-        <v>17.89116063448317</v>
+        <v>2.907313603103515</v>
       </c>
       <c r="F6" t="n">
-        <v>15.59864920617222</v>
+        <v>2.534780496002985</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>56.16941060816891</v>
+        <v>9.127529223827448</v>
       </c>
       <c r="D7" t="n">
-        <v>28.96979860242343</v>
+        <v>4.707592272893808</v>
       </c>
       <c r="E7" t="n">
-        <v>17.89116063448317</v>
+        <v>2.907313603103515</v>
       </c>
       <c r="F7" t="n">
-        <v>15.59864920617222</v>
+        <v>2.534780496002985</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>40.30903002100855</v>
+        <v>6.550217378413889</v>
       </c>
       <c r="D8" t="n">
-        <v>46.50776756554772</v>
+        <v>7.557512229401505</v>
       </c>
       <c r="E8" t="n">
-        <v>17.89116063448317</v>
+        <v>2.907313603103515</v>
       </c>
       <c r="F8" t="n">
-        <v>15.59864920617222</v>
+        <v>2.534780496002985</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>46.06945058803782</v>
+        <v>7.486285720556146</v>
       </c>
       <c r="D9" t="n">
-        <v>46.18014586467794</v>
+        <v>7.504273703010165</v>
       </c>
       <c r="E9" t="n">
-        <v>17.89116063448317</v>
+        <v>2.907313603103515</v>
       </c>
       <c r="F9" t="n">
-        <v>15.59864920617222</v>
+        <v>2.534780496002985</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>59.34854673873658</v>
+        <v>9.644138845044695</v>
       </c>
       <c r="D10" t="n">
-        <v>41.36725758374611</v>
+        <v>6.722179357358743</v>
       </c>
       <c r="E10" t="n">
-        <v>17.89116063448317</v>
+        <v>2.907313603103515</v>
       </c>
       <c r="F10" t="n">
-        <v>15.59864920617222</v>
+        <v>2.534780496002985</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>52.63194319953107</v>
+        <v>8.552690769923798</v>
       </c>
       <c r="D11" t="n">
-        <v>33.86741720449491</v>
+        <v>5.503455295730424</v>
       </c>
       <c r="E11" t="n">
-        <v>17.89116063448317</v>
+        <v>2.907313603103515</v>
       </c>
       <c r="F11" t="n">
-        <v>15.59864920617222</v>
+        <v>2.534780496002985</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>26.75757490024069</v>
+        <v>4.348105921289112</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7071067811865476</v>
+        <v>0.114904851942814</v>
       </c>
       <c r="E12" t="n">
-        <v>17.89116063448317</v>
+        <v>2.907313603103515</v>
       </c>
       <c r="F12" t="n">
-        <v>15.59864920617222</v>
+        <v>2.534780496002985</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>14.83276288609208</v>
+        <v>2.410323968989963</v>
       </c>
       <c r="D13" t="n">
-        <v>13.36405719425646</v>
+        <v>2.171659294066675</v>
       </c>
       <c r="E13" t="n">
-        <v>17.89116063448317</v>
+        <v>2.907313603103515</v>
       </c>
       <c r="F13" t="n">
-        <v>15.59864920617222</v>
+        <v>2.534780496002985</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>18.24519740812372</v>
+        <v>2.964844578820104</v>
       </c>
       <c r="D14" t="n">
-        <v>9.219544457292887</v>
+        <v>1.498175974310094</v>
       </c>
       <c r="E14" t="n">
-        <v>17.89116063448317</v>
+        <v>2.907313603103515</v>
       </c>
       <c r="F14" t="n">
-        <v>15.59864920617222</v>
+        <v>2.534780496002985</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>4.018598795545702</v>
+        <v>0.6530223042761766</v>
       </c>
       <c r="D15" t="n">
-        <v>10.89409660728639</v>
+        <v>1.770290698684039</v>
       </c>
       <c r="E15" t="n">
-        <v>17.89116063448317</v>
+        <v>2.907313603103515</v>
       </c>
       <c r="F15" t="n">
-        <v>15.59864920617222</v>
+        <v>2.534780496002985</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
